--- a/series_data/infinite-trip/series_log.xlsx
+++ b/series_data/infinite-trip/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -814,6 +814,226 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>C:\Users\ihsan\Desktop\Antigravity\Projects\Youtube\output\series\infinite-trip\episodes\ep01\shots\shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-17 17:44</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c4dbf1122f1a418f4df611ae5f75d566_1781718254.mp4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep02/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-17 17:48</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1d36db26b04d7a1b11b39a097860cb25_1781718474.mp4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep02/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-17 17:50</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2935c059c13d9acd272e68c6a300fd9e_1781718606.mp4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep02/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-17 17:52</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/38034c3ff37cde5e30392fbed7797fcc_1781718732.mp4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep02/shots/shot_04.mp4</t>
         </is>
       </c>
     </row>

--- a/series_data/infinite-trip/series_log.xlsx
+++ b/series_data/infinite-trip/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1037,6 +1037,226 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/aed40b82b25ea33668f7a208e0b76345_1781805938.mp4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:08</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/18c84c26582f01a746d16ce77d24fccf_1781806081.mp4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep03/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3ab2bb4f1b66225ac50fb100ab533765_1781806207.mp4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep03/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/56a1066b88d54b56d08dd1e305c8578b_1781806344.mp4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep03/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/infinite-trip/series_log.xlsx
+++ b/series_data/infinite-trip/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1257,6 +1257,226 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:59</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a677d7812bc85828ccb2278ddf539fac_1781888384.mp4</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-19 17:02</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/66ec027dcdd6fb6a382b5e3458d12894_1781888512.mp4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep04/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-19 17:04</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/267d94ede2b7ace8004ed80886e8ad21_1781888650.mp4</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep04/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-19 17:06</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/61b3dc3bed4e1f66d60413e1fb95090f_1781888783.mp4</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep04/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/infinite-trip/series_log.xlsx
+++ b/series_data/infinite-trip/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1477,6 +1477,226 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-20 16:12</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6fece9b1f5049cf92ff308ed8d057923_1781971958.mp4</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-20 16:15</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4059e0bbbacb04ea4eecdb97e6b4ed18_1781972092.mp4</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep05/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-20 16:17</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c47c2ebba5550534fd1ab75360f58dc2_1781972257.mp4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep05/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-20 16:20</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5b63b011be5fbe34b68cb5a32a76146b_1781972415.mp4</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep05/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/infinite-trip/series_log.xlsx
+++ b/series_data/infinite-trip/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1697,6 +1697,226 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-22 17:52</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ff018973c08404462b5d30b9412535a1_1782150760.mp4</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep06/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-22 17:55</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/686bf518394a150f30733f14efb89466_1782150919.mp4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep06/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-22 17:57</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6bc7055ab37d0f7cdf91885597bf28c9_1782151063.mp4</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep06/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-22 17:59</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/33f19c77588f53cd96921e02f8eeaf9c_1782151180.mp4</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep06/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/infinite-trip/series_log.xlsx
+++ b/series_data/infinite-trip/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1917,6 +1917,226 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:57</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/08274a841d3fe57d9a72cb8fb1957a80_1782154636.mp4</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep07/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:59</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f99eefef3d93b63c0f440d1d1faf2c10_1782154780.mp4</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep07/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-22 19:02</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/18b551a0256ee6e267b91e1378a37434_1782154945.mp4</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep07/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-22 19:04</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e1456fc494430b996c8a2c82b1f1790a_1782155088.mp4</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep07/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/infinite-trip/series_log.xlsx
+++ b/series_data/infinite-trip/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2137,6 +2137,226 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/02d4776bcdb141354898e75976e28c0f_1782234039.mp4</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:05</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b70af1526289b34d2e00327312b5a991_1782234282.mp4</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep08/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:08</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b9a632b0149d9d135c71c0ec906840ee_1782234475.mp4</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep08/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:10</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/01bec5af9648c4b1cfa661910ea01df2_1782234626.mp4</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep08/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/infinite-trip/series_log.xlsx
+++ b/series_data/infinite-trip/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2357,6 +2357,226 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:51</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b80bdb5d6f0780eccc70c849b8d8fe8f_1782319904.mp4</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep09/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:54</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/91c206cf24f3c7929ae3a21e11b96107_1782320032.mp4</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep09/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:56</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/faabf2b44504ab5a6b0ae348180e1dbd_1782320163.mp4</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep09/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:58</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0f9a89e62ad2f5ad7b1465cba853572d_1782320296.mp4</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep09/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/infinite-trip/series_log.xlsx
+++ b/series_data/infinite-trip/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2577,6 +2577,226 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-25 17:00</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/246a30cc645a7dcffc9c977284f980c1_1782406793.mp4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep10/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-25 17:02</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a70cc6311f3b1f46d99063d587e3c8a7_1782406961.mp4</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep10/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-25 17:05</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/609f85f580db9bd751c9a9ff420e3f47_1782407102.mp4</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep10/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-25 17:08</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/dccd7a525b4e55b9e9079a125eef7227_1782407326.mp4</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep10/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/infinite-trip/series_log.xlsx
+++ b/series_data/infinite-trip/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2797,6 +2797,226 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:04</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/082cd547b430a8704bd790bfd8318f77_1783022570.mp4</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>C:\Users\ihsan\Desktop\Antigravity\Projects\Youtube\output\series\infinite-trip\episodes\ep11\shots\shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:07</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d9ef0b8bc010585ff040478c8da77baa_1783022848.mp4</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>C:\Users\ihsan\Desktop\Antigravity\Projects\Youtube\output\series\infinite-trip\episodes\ep11\shots\shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:12</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/41f0769826ab2bd19f17a47985dfa740_1783023120.mp4</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>C:\Users\ihsan\Desktop\Antigravity\Projects\Youtube\output\series\infinite-trip\episodes\ep11\shots\shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f8f1f51ea19eb452a72ab621fbe8caa6_1783023248.mp4</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>C:\Users\ihsan\Desktop\Antigravity\Projects\Youtube\output\series\infinite-trip\episodes\ep11\shots\shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/infinite-trip/series_log.xlsx
+++ b/series_data/infinite-trip/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3017,6 +3017,226 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-05 15:57</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7498c8ef063e4230952fe2862050048c_1783267008.mp4</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep12/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-05 16:23</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/388d0dd790e12cda4618405288cacfb0_1783268552.mp4</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep12/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-05 16:32</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7dcaf0dabbaf18ecf3059667afa75564_1783269088.mp4</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep12/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-05 16:34</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a8c15339edf0e1b6a519896695381505_1783269249.mp4</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep12/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/infinite-trip/series_log.xlsx
+++ b/series_data/infinite-trip/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3237,6 +3237,226 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-06 17:22</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a8040a6e6e1125425fb55074a4cb5677_1783358500.mp4</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep13/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-06 17:25</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5542d7986c8ecde10cf46153d1e18196_1783358723.mp4</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep13/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-06 17:28</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1103146c325dc5ad0e6295049fd585d3_1783358888.mp4</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep13/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-06 17:32</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/57e573423b7a00320050ce1e840fdbb9_1783359129.mp4</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep13/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/infinite-trip/series_log.xlsx
+++ b/series_data/infinite-trip/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3457,6 +3457,226 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:48</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/31854a8316c9ecd920b5a63f04ef10cd_1783442893.mp4</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep14/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:51</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9dd74cde51497e4ed9a0bab492f594f0_1783443048.mp4</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep14/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:53</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1b4368f181b27c73ee1ae807206ef70c_1783443199.mp4</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep14/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:57</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a59dc5ff9032baed4f8b434dac140f19_1783443408.mp4</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep14/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/infinite-trip/series_log.xlsx
+++ b/series_data/infinite-trip/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3677,6 +3677,226 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:16</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0f8e8dba5184a9c5a2b3876d77cd82f5_1783527349.mp4</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep15/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:22</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9471ad28d05a37231ec9902f91d563c1_1783527701.mp4</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep15/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/44be9e33f6fe471c6dccf05832fb04b2_1783527957.mp4</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep15/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:29</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0b5f9decc6a275f6f9cd2951ec5e1ac0_1783528160.mp4</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/infinite-trip/episodes/ep15/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
